--- a/VerveStacks_FRA_grids_syn_5/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_FRA_grids_syn_5/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_FRA_grids_syn_5\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{57521227-B2FB-4D0F-B4DC-3F4BEE9A5A3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{968735A1-7948-46B2-8570-C5F36B0272DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{1E5A1470-A7D2-4641-AFFA-526DC3F59E07}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{5E7CA8F7-33C7-4FB0-8C8F-318D9190CE24}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1333,7 +1333,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECD567D1-72B3-49C0-BCC1-AEB7F09A77B5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13B56F4F-F7A1-4A08-AD3D-8B642EF54F27}">
   <dimension ref="B3:L109"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_FRA_grids_syn_5/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_FRA_grids_syn_5/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_FRA_grids_syn_5\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{968735A1-7948-46B2-8570-C5F36B0272DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{91FCA4CC-DF37-46B9-99CA-1940DC710C3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{5E7CA8F7-33C7-4FB0-8C8F-318D9190CE24}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{CAD63841-3A21-4F1F-99BF-C62289CCBC3E}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1333,7 +1333,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13B56F4F-F7A1-4A08-AD3D-8B642EF54F27}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DF23F63-24B4-42E5-BC77-18D355FD9582}">
   <dimension ref="B3:L109"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_FRA_grids_syn_5/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_FRA_grids_syn_5/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_FRA_grids_syn_5\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{91FCA4CC-DF37-46B9-99CA-1940DC710C3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{455F1F6F-3546-4D30-A766-7B37451B4C91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{CAD63841-3A21-4F1F-99BF-C62289CCBC3E}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{56E775C6-B440-4947-8636-F7F2B3374C35}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1333,7 +1333,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DF23F63-24B4-42E5-BC77-18D355FD9582}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D9E12E4-A046-4EE8-AE46-1BFE40541C64}">
   <dimension ref="B3:L109"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_FRA_grids_syn_5/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_FRA_grids_syn_5/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_FRA_grids_syn_5\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{455F1F6F-3546-4D30-A766-7B37451B4C91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{37F3958F-F556-4F0D-AF72-1648A24F6571}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{56E775C6-B440-4947-8636-F7F2B3374C35}"/>
+    <workbookView xWindow="4043" yWindow="4043" windowWidth="21599" windowHeight="12682" xr2:uid="{AFDBABA9-94E0-4F5B-97EF-C4186889648F}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1333,7 +1333,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D9E12E4-A046-4EE8-AE46-1BFE40541C64}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D667B0F-93FA-4B46-BB76-FD583715E360}">
   <dimension ref="B3:L109"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
